--- a/activityAnalysis/US_Champs.xlsx
+++ b/activityAnalysis/US_Champs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachaelnaphtal/Documents/JudgingAnalysis/activityAnalysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDCDA4B-96C0-5148-92D6-5B6FAEB1E07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B4F9EF-77FE-4A49-B5E8-B8221734A89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15420" yWindow="760" windowWidth="13000" windowHeight="16620" xr2:uid="{891C92EF-756F-2947-96D2-AD9E27690499}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4491" uniqueCount="528">
   <si>
     <t>Name</t>
   </si>
@@ -1650,7 +1650,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1719,6 +1719,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1740,7 +1746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1751,6 +1757,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6819,8 +6826,12 @@
         <v>45</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
         <v>21</v>
@@ -11640,8 +11651,12 @@
         <v>9</v>
       </c>
       <c r="O43" s="2"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
+      <c r="P43" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="R43" s="2"/>
       <c r="S43" s="2" t="s">
         <v>254</v>
@@ -15288,8 +15303,12 @@
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
-      <c r="S62" s="2"/>
-      <c r="T62" s="2"/>
+      <c r="S62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="U62" s="2"/>
       <c r="V62" s="2" t="s">
         <v>88</v>
@@ -15409,8 +15428,12 @@
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
-      <c r="S63" s="2"/>
-      <c r="T63" s="2"/>
+      <c r="S63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="U63" s="2"/>
       <c r="V63" s="2" t="s">
         <v>295</v>
@@ -15512,8 +15535,12 @@
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
-      <c r="S64" s="2"/>
-      <c r="T64" s="2"/>
+      <c r="S64" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="U64" s="2"/>
       <c r="V64" s="2" t="s">
         <v>92</v>
@@ -15619,8 +15646,12 @@
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
-      <c r="S65" s="2"/>
-      <c r="T65" s="2"/>
+      <c r="S65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="U65" s="2"/>
       <c r="V65" s="2" t="s">
         <v>13</v>
@@ -15722,8 +15753,12 @@
       <c r="P66" s="2"/>
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
-      <c r="S66" s="2"/>
-      <c r="T66" s="2"/>
+      <c r="S66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="U66" s="2"/>
       <c r="V66" s="2" t="s">
         <v>126</v>
@@ -15806,8 +15841,12 @@
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
+      <c r="D67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -15825,8 +15864,12 @@
       <c r="P67" s="2"/>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
-      <c r="S67" s="2"/>
-      <c r="T67" s="2"/>
+      <c r="S67" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="U67" s="2"/>
       <c r="V67" s="2" t="s">
         <v>19</v>
@@ -15909,8 +15952,12 @@
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
+      <c r="D68" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -16004,8 +16051,12 @@
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
+      <c r="D69" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -16156,8 +16207,12 @@
         <v>185</v>
       </c>
       <c r="AJ70" s="2"/>
-      <c r="AK70" s="2"/>
-      <c r="AL70" s="2"/>
+      <c r="AK70" t="s">
+        <v>28</v>
+      </c>
+      <c r="AL70" s="2" t="s">
+        <v>362</v>
+      </c>
       <c r="AM70" s="2"/>
       <c r="AN70" t="s">
         <v>66</v>
@@ -16251,8 +16306,12 @@
         <v>32</v>
       </c>
       <c r="AJ71" s="2"/>
-      <c r="AK71" s="2"/>
-      <c r="AL71" s="2"/>
+      <c r="AK71" t="s">
+        <v>90</v>
+      </c>
+      <c r="AL71" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AM71" s="2"/>
       <c r="AN71" s="2"/>
       <c r="AO71" s="2"/>
@@ -16342,8 +16401,12 @@
         <v>32</v>
       </c>
       <c r="AJ72" s="2"/>
-      <c r="AK72" s="2"/>
-      <c r="AL72" s="2"/>
+      <c r="AK72" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL72" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="AM72" s="2"/>
       <c r="AN72" s="2"/>
       <c r="AO72" s="2"/>
@@ -16433,8 +16496,12 @@
         <v>30</v>
       </c>
       <c r="AJ73" s="2"/>
-      <c r="AK73" s="2"/>
-      <c r="AL73" s="2"/>
+      <c r="AK73" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL73" s="2" t="s">
+        <v>363</v>
+      </c>
       <c r="AM73" s="2"/>
       <c r="AN73" s="2"/>
       <c r="AO73" s="2"/>
@@ -16588,8 +16655,12 @@
         <v>154</v>
       </c>
       <c r="AA75" s="2"/>
-      <c r="AB75" s="2"/>
-      <c r="AC75" s="2"/>
+      <c r="AB75" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC75" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="AD75" s="2"/>
       <c r="AE75" t="s">
         <v>282</v>
@@ -16663,8 +16734,12 @@
         <v>401</v>
       </c>
       <c r="AA76" s="2"/>
-      <c r="AB76" s="2"/>
-      <c r="AC76" s="2"/>
+      <c r="AB76" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="AC76" s="2" t="s">
+        <v>375</v>
+      </c>
       <c r="AD76" s="2"/>
       <c r="AE76" t="s">
         <v>316</v>
@@ -16731,11 +16806,19 @@
         <v>301</v>
       </c>
       <c r="X77" s="2"/>
-      <c r="Y77" s="2"/>
-      <c r="Z77" s="2"/>
+      <c r="Y77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z77" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="AA77" s="2"/>
-      <c r="AB77" s="2"/>
-      <c r="AC77" s="2"/>
+      <c r="AB77" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC77" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="AD77" s="2"/>
       <c r="AE77" s="2" t="s">
         <v>402</v>
@@ -16802,14 +16885,26 @@
         <v>306</v>
       </c>
       <c r="X78" s="2"/>
-      <c r="Y78" s="2"/>
-      <c r="Z78" s="2"/>
+      <c r="Y78" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z78" s="2" t="s">
+        <v>337</v>
+      </c>
       <c r="AA78" s="2"/>
-      <c r="AB78" s="2"/>
-      <c r="AC78" s="2"/>
+      <c r="AB78" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC78" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="AD78" s="2"/>
-      <c r="AE78" s="2"/>
-      <c r="AF78" s="2"/>
+      <c r="AE78" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF78" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="AG78" s="2"/>
       <c r="AH78" s="2" t="s">
         <v>263</v>
@@ -16869,17 +16964,33 @@
         <v>83</v>
       </c>
       <c r="X79" s="2"/>
-      <c r="Y79" s="2"/>
-      <c r="Z79" s="2"/>
+      <c r="Y79" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z79" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AA79" s="2"/>
-      <c r="AB79" s="2"/>
-      <c r="AC79" s="2"/>
+      <c r="AB79" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC79" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AD79" s="2"/>
-      <c r="AE79" s="2"/>
-      <c r="AF79" s="2"/>
+      <c r="AE79" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF79" s="2" t="s">
+        <v>375</v>
+      </c>
       <c r="AG79" s="2"/>
-      <c r="AH79" s="2"/>
-      <c r="AI79" s="2"/>
+      <c r="AH79" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI79" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="AJ79" s="2"/>
       <c r="AK79" s="2"/>
       <c r="AL79" s="2"/>
@@ -16935,14 +17046,26 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
       <c r="AA80" s="2"/>
-      <c r="AB80" s="2"/>
-      <c r="AC80" s="2"/>
+      <c r="AB80" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC80" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="AD80" s="2"/>
-      <c r="AE80" s="2"/>
-      <c r="AF80" s="2"/>
+      <c r="AE80" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF80" s="2" t="s">
+        <v>337</v>
+      </c>
       <c r="AG80" s="2"/>
-      <c r="AH80" s="2"/>
-      <c r="AI80" s="2"/>
+      <c r="AH80" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI80" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="AJ80" s="2"/>
       <c r="AK80" s="2"/>
       <c r="AL80" s="2"/>
@@ -16998,14 +17121,26 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
       <c r="AA81" s="2"/>
-      <c r="AB81" s="2"/>
-      <c r="AC81" s="2"/>
+      <c r="AB81" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC81" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="AD81" s="2"/>
-      <c r="AE81" s="2"/>
-      <c r="AF81" s="2"/>
+      <c r="AE81" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF81" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="AG81" s="2"/>
-      <c r="AH81" s="2"/>
-      <c r="AI81" s="2"/>
+      <c r="AH81" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI81" s="2" t="s">
+        <v>366</v>
+      </c>
       <c r="AJ81" s="2"/>
       <c r="AK81" s="2"/>
       <c r="AL81" s="2"/>
@@ -17067,8 +17202,12 @@
       <c r="AE82" s="2"/>
       <c r="AF82" s="2"/>
       <c r="AG82" s="2"/>
-      <c r="AH82" s="2"/>
-      <c r="AI82" s="2"/>
+      <c r="AH82" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI82" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="AJ82" s="2"/>
       <c r="AK82" s="2"/>
       <c r="AL82" s="2"/>
@@ -17124,8 +17263,12 @@
       <c r="AE83" s="2"/>
       <c r="AF83" s="2"/>
       <c r="AG83" s="2"/>
-      <c r="AH83" s="2"/>
-      <c r="AI83" s="2"/>
+      <c r="AH83" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI83" s="2" t="s">
+        <v>362</v>
+      </c>
       <c r="AJ83" s="2"/>
       <c r="AK83" s="2"/>
       <c r="AL83" s="2"/>
@@ -17564,8 +17707,12 @@
       <c r="S91" s="2"/>
       <c r="T91" s="2"/>
       <c r="U91" s="2"/>
-      <c r="V91" s="2"/>
-      <c r="W91" s="2"/>
+      <c r="V91" t="s">
+        <v>13</v>
+      </c>
+      <c r="W91" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="X91" s="2"/>
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
@@ -17617,8 +17764,12 @@
       <c r="S92" s="2"/>
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
-      <c r="V92" s="2"/>
-      <c r="W92" s="2"/>
+      <c r="V92" t="s">
+        <v>92</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="X92" s="2"/>
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
@@ -17670,8 +17821,12 @@
       <c r="S93" s="2"/>
       <c r="T93" s="2"/>
       <c r="U93" s="2"/>
-      <c r="V93" s="2"/>
-      <c r="W93" s="2"/>
+      <c r="V93" t="s">
+        <v>118</v>
+      </c>
+      <c r="W93" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="X93" s="2"/>
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
@@ -17723,8 +17878,12 @@
       <c r="S94" s="2"/>
       <c r="T94" s="2"/>
       <c r="U94" s="2"/>
-      <c r="V94" s="2"/>
-      <c r="W94" s="2"/>
+      <c r="V94" t="s">
+        <v>66</v>
+      </c>
+      <c r="W94" s="2" t="s">
+        <v>363</v>
+      </c>
       <c r="X94" s="2"/>
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
@@ -17776,8 +17935,12 @@
       <c r="S95" s="2"/>
       <c r="T95" s="2"/>
       <c r="U95" s="2"/>
-      <c r="V95" s="2"/>
-      <c r="W95" s="2"/>
+      <c r="V95" t="s">
+        <v>58</v>
+      </c>
+      <c r="W95" s="2" t="s">
+        <v>366</v>
+      </c>
       <c r="X95" s="2"/>
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
@@ -17829,8 +17992,12 @@
       <c r="S96" s="2"/>
       <c r="T96" s="2"/>
       <c r="U96" s="2"/>
-      <c r="V96" s="2"/>
-      <c r="W96" s="2"/>
+      <c r="V96" t="s">
+        <v>88</v>
+      </c>
+      <c r="W96" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="X96" s="2"/>
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
@@ -17882,8 +18049,12 @@
       <c r="S97" s="2"/>
       <c r="T97" s="2"/>
       <c r="U97" s="2"/>
-      <c r="V97" s="2"/>
-      <c r="W97" s="2"/>
+      <c r="V97" t="s">
+        <v>64</v>
+      </c>
+      <c r="W97" s="2" t="s">
+        <v>366</v>
+      </c>
       <c r="X97" s="2"/>
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
